--- a/agricola/cards/data/revised_cards.xlsx
+++ b/agricola/cards/data/revised_cards.xlsx
@@ -20281,7 +20281,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>1 Wood</t>
+          <t>2 Wood</t>
         </is>
       </c>
       <c r="H96" t="n">
